--- a/data/30days_result.xlsx
+++ b/data/30days_result.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,257 +440,205 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>172</v>
+        <v>240</v>
       </c>
       <c r="C2" t="n">
-        <v>23970</v>
+        <v>71677</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>黄亚康</t>
+          <t>乐天</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="C3" t="n">
-        <v>9000</v>
+        <v>31548</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>龙航宇</t>
+          <t>庄允贵</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="C4" t="n">
-        <v>15399</v>
+        <v>43404</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>黄卓文</t>
+          <t>龚航</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C5" t="n">
-        <v>13319</v>
+        <v>56557</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>池镇海</t>
+          <t>黄卓文</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="C6" t="n">
-        <v>27335</v>
+        <v>24838</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>龚航</t>
+          <t>黄亚康</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="C7" t="n">
-        <v>318410</v>
+        <v>8154</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>马可一</t>
+          <t>黄祺茂</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="C8" t="n">
-        <v>4632</v>
+        <v>4418</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>文精明</t>
+          <t>池镇海</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
-        <v>347</v>
+        <v>88483</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>黄祺茂</t>
+          <t>文精明</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C10" t="n">
-        <v>2733</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>庄允贵</t>
+          <t>龙航宇</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>26470</v>
+        <v>5136</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>乐天</t>
+          <t>刘金龙</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>8105</v>
+        <v>15690</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>龚欣柔</t>
+          <t>王昕</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>6166</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>宋智刚</t>
+          <t>陈祥芝</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C14" t="n">
-        <v>101800</v>
+        <v>51034</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>王昕</t>
+          <t>曾小芬</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>73108</v>
+        <v>3891</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>刘金龙</t>
+          <t>王晶</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>7331</v>
+        <v>792</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>曾小芬</t>
+          <t>叶小凤</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>24867</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>刘臣</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>6</v>
-      </c>
-      <c r="C18" t="n">
-        <v>13949</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>陈祥芝</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>3</v>
-      </c>
-      <c r="C19" t="n">
-        <v>5136</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>叶小凤</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>3</v>
-      </c>
-      <c r="C20" t="n">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>王晶</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>2</v>
-      </c>
-      <c r="C21" t="n">
-        <v>316</v>
+        <v>645</v>
       </c>
     </row>
   </sheetData>
